--- a/Assets/c#/Dialog/teacher.xlsx
+++ b/Assets/c#/Dialog/teacher.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/allen/Documents/GitHub/WhiteNight/Assets/c#/Dialog/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537050F4-F377-5846-9537-E4F618399E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F90187B-18C2-C141-8D87-3E01F8640DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
   <si>
     <t>day</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -101,6 +101,36 @@
   <si>
     <t>ap_2</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ap_3</t>
+  </si>
+  <si>
+    <t>ap_4</t>
+  </si>
+  <si>
+    <t>ap_5</t>
+  </si>
+  <si>
+    <t>ap_6</t>
+  </si>
+  <si>
+    <t>ap_7</t>
+  </si>
+  <si>
+    <t>ap_8</t>
+  </si>
+  <si>
+    <t>ap_9</t>
+  </si>
+  <si>
+    <t>ap_10</t>
+  </si>
+  <si>
+    <t>ap_11</t>
+  </si>
+  <si>
+    <t>ap_12</t>
   </si>
 </sst>
 </file>
@@ -425,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA6E35B-75A1-451F-BF9F-5CB9243878FB}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="14.5" customWidth="1"/>
@@ -585,6 +615,296 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>6</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10">
+        <v>7</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11">
+        <v>8</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12">
+        <v>9</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14">
+        <v>11</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15">
+        <v>12</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
